--- a/DanhSachNhanVien.xlsx
+++ b/DanhSachNhanVien.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\CoffeeManagement\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0659724E-146D-4FAC-B40F-841DB676BA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="4320" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhanVien" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -44,31 +52,28 @@
     <t>UserID</t>
   </si>
   <si>
-    <t>Nguyễn</t>
+    <t>s</t>
   </si>
   <si>
     <t>An</t>
   </si>
   <si>
-    <t>Nguyễn An</t>
-  </si>
-  <si>
-    <t>0909000001</t>
+    <t>s An</t>
+  </si>
+  <si>
+    <t>0909000009</t>
   </si>
   <si>
     <t>Đang làm</t>
   </si>
   <si>
-    <t>07/12/2025</t>
+    <t>08/12/2025</t>
   </si>
   <si>
     <t>Trần</t>
   </si>
   <si>
-    <t>Bình</t>
-  </si>
-  <si>
-    <t>Trần Bình</t>
+    <t>Trần s</t>
   </si>
   <si>
     <t>0909000002</t>
@@ -83,7 +88,10 @@
     <t>Lê Cường</t>
   </si>
   <si>
-    <t>0909000003</t>
+    <t>0909003003</t>
+  </si>
+  <si>
+    <t>Trống</t>
   </si>
   <si>
     <t>Phạm</t>
@@ -108,16 +116,19 @@
   </si>
   <si>
     <t>0909000005</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -137,7 +148,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD3D3D3" tint="0"/>
+        <fgColor rgb="FFD3D3D3"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,40 +162,363 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.9968991960798" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.5125013078962" customWidth="1"/>
-    <col min="5" max="5" width="15.2580130440848" customWidth="1"/>
-    <col min="6" max="6" width="12.925424848284" customWidth="1"/>
-    <col min="7" max="7" width="16.7171609061105" customWidth="1"/>
-    <col min="8" max="8" width="17.5407278878348" customWidth="1"/>
-    <col min="9" max="9" width="17.2990286690848" customWidth="1"/>
-    <col min="10" max="10" width="9.16182272774833" customWidth="1"/>
+    <col min="1" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -216,152 +550,167 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2">
-        <v>45301</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="0">
+      <c r="G2" s="3">
+        <v>45566</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3">
+        <v>45414</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3">
+        <v>45566</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2">
-        <v>45327</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="0">
-        <v>2</v>
+      <c r="G5" s="3">
+        <v>45294</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2">
+        <v>4</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="0" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="2">
-        <v>45342</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2">
-        <v>45352</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>45366</v>
       </c>
-      <c r="I6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="0">
-        <v>5</v>
+      <c r="H6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DanhSachNhanVien.xlsx
+++ b/DanhSachNhanVien.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\CoffeeManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\CoffeeManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0659724E-146D-4FAC-B40F-841DB676BA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6054D2-9334-4133-BA7F-3BEF09EC8086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhanVien" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -52,33 +52,36 @@
     <t>UserID</t>
   </si>
   <si>
-    <t>s</t>
+    <t>Nguyễn</t>
   </si>
   <si>
     <t>An</t>
   </si>
   <si>
-    <t>s An</t>
-  </si>
-  <si>
-    <t>0909000009</t>
-  </si>
-  <si>
-    <t>Đang làm</t>
-  </si>
-  <si>
-    <t>08/12/2025</t>
+    <t>Nguyễn An</t>
+  </si>
+  <si>
+    <t>0909000001</t>
+  </si>
+  <si>
+    <t>Đang làm việc</t>
+  </si>
+  <si>
+    <t>12/12/2025</t>
   </si>
   <si>
     <t>Trần</t>
   </si>
   <si>
-    <t>Trần s</t>
+    <t>Trần Bình</t>
   </si>
   <si>
     <t>0909000002</t>
   </si>
   <si>
+    <t>Trống lịch</t>
+  </si>
+  <si>
     <t>Lê</t>
   </si>
   <si>
@@ -88,12 +91,6 @@
     <t>Lê Cường</t>
   </si>
   <si>
-    <t>0909003003</t>
-  </si>
-  <si>
-    <t>Trống</t>
-  </si>
-  <si>
     <t>Phạm</t>
   </si>
   <si>
@@ -116,6 +113,15 @@
   </si>
   <si>
     <t>0909000005</t>
+  </si>
+  <si>
+    <t>Trân</t>
+  </si>
+  <si>
+    <t>0909003333</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>5</t>
@@ -128,7 +134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -165,12 +171,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -199,39 +205,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -283,7 +289,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -394,6 +400,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -402,13 +415,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -473,31 +479,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -506,19 +492,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" customWidth="1"/>
+    <col min="1" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -570,7 +555,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="3">
-        <v>45566</v>
+        <v>45301</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -582,7 +567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -590,7 +575,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -599,14 +584,12 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
-        <v>45414</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>45327</v>
+      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
@@ -614,63 +597,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3">
-        <v>45566</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="2">
-        <v>3</v>
+        <v>45708</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3">
+        <v>46003</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
-        <v>45294</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>45352</v>
+      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
@@ -678,36 +657,34 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
         <v>45366</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>32</v>
+      <c r="J6" s="2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/DanhSachNhanVien.xlsx
+++ b/DanhSachNhanVien.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\CoffeeManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\CoffeeManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6054D2-9334-4133-BA7F-3BEF09EC8086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60988E43-3211-4577-9FD7-F5FDFAD5F9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhanVien" sheetId="1" r:id="rId1"/>
@@ -134,7 +134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -171,12 +171,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -195,9 +195,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -235,7 +235,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -341,7 +341,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -483,7 +483,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -492,18 +492,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="1" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -535,7 +535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -567,7 +567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -597,7 +597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -627,7 +627,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -657,7 +657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
